--- a/MOMENTUM_DB_2 copy/Stocks/Nifty_500_2025_Apr_20_stocks_results/momentum_20230101_20230701.xlsx
+++ b/MOMENTUM_DB_2 copy/Stocks/Nifty_500_2025_Apr_20_stocks_results/momentum_20230101_20230701.xlsx
@@ -1229,37 +1229,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EXIDEIND</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>59.50413223140496</v>
+        <v>58.67768595041323</v>
       </c>
       <c r="C19" t="n">
-        <v>39.66942148760331</v>
+        <v>41.32231404958678</v>
       </c>
       <c r="D19" t="n">
-        <v>27.0443767813177</v>
+        <v>29.63293419863571</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>INE302A01020</t>
+          <t>INE003A01024</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G19" t="n">
-        <v>-19.83471074380165</v>
+        <v>-17.35537190082645</v>
       </c>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="I19" t="n">
         <v>91</v>
       </c>
       <c r="J19" t="n">
-        <v>236.7</v>
+        <v>1873.85</v>
       </c>
       <c r="K19" t="n">
         <v>18</v>
@@ -1273,37 +1273,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>EXIDEIND</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>58.67768595041323</v>
+        <v>59.50413223140496</v>
       </c>
       <c r="C20" t="n">
-        <v>41.32231404958678</v>
+        <v>39.66942148760331</v>
       </c>
       <c r="D20" t="n">
-        <v>29.63293419863571</v>
+        <v>27.0443767813177</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>INE003A01024</t>
+          <t>INE302A01020</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="G20" t="n">
-        <v>-17.35537190082645</v>
+        <v>-19.83471074380165</v>
       </c>
       <c r="H20" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="I20" t="n">
         <v>91</v>
       </c>
       <c r="J20" t="n">
-        <v>1873.85</v>
+        <v>236.7</v>
       </c>
       <c r="K20" t="n">
         <v>19</v>
